--- a/RACE.xlsx
+++ b/RACE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF5E114-E12D-4027-BC78-68926E774FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{847B4EC6-6470-4464-89DE-83BE46580EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{175A7000-C55F-4819-AB9F-1BE087EDC274}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{175A7000-C55F-4819-AB9F-1BE087EDC274}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
   <si>
     <t>Ferrari</t>
   </si>
@@ -91,9 +91,6 @@
   </si>
   <si>
     <t>IR</t>
-  </si>
-  <si>
-    <t>Q424</t>
   </si>
   <si>
     <t>Notes</t>
@@ -167,21 +164,61 @@
   <si>
     <t>Other</t>
   </si>
+  <si>
+    <t>FY25</t>
+  </si>
+  <si>
+    <t>EPS</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>Car Shipments Growth</t>
+  </si>
+  <si>
+    <t>Cars Rev Growth</t>
+  </si>
+  <si>
+    <t>Sponsors Rev Growth</t>
+  </si>
+  <si>
+    <t>Other Growth</t>
+  </si>
+  <si>
+    <t>Revenue Growth</t>
+  </si>
+  <si>
+    <t>Gross Margin</t>
+  </si>
+  <si>
+    <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>Tax Rate</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -218,6 +255,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -236,27 +288,37 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -269,6 +331,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>151281</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>108416</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>16810</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>43882</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C03E5773-E881-C95E-052B-2CE80B709854}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="409016" y="2383210"/>
+          <a:ext cx="7194176" cy="1722804"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -608,7 +719,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="2">
-        <v>399</v>
+        <v>296.39999999999998</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -616,10 +727,10 @@
         <v>3</v>
       </c>
       <c r="H3" s="3">
-        <v>179.99199999999999</v>
+        <v>178.125</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>18</v>
+      <c r="I3" s="9" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -631,7 +742,7 @@
       </c>
       <c r="H4" s="3">
         <f>+H2*H3</f>
-        <v>71816.80799999999</v>
+        <v>52796.249999999993</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -642,11 +753,11 @@
         <v>5</v>
       </c>
       <c r="H5" s="3">
-        <f>1742.214+25.006</f>
-        <v>1767.22</v>
+        <f>1467.711+78.085</f>
+        <v>1545.796</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>18</v>
+      <c r="I5" s="9" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -654,48 +765,48 @@
         <v>6</v>
       </c>
       <c r="H6" s="3">
-        <v>3351.8879999999999</v>
+        <v>2884.22</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>18</v>
+      <c r="I6" s="9" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B7" s="2" t="s">
-        <v>21</v>
+      <c r="B7" s="11" t="s">
+        <v>20</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="H7" s="3">
         <f>+H4-H5+H6</f>
-        <v>73401.475999999995</v>
+        <v>54134.673999999992</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B12" s="4"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B13" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -703,6 +814,7 @@
     <hyperlink ref="B5" r:id="rId1" xr:uid="{39BD3AD8-1DB2-4519-B716-EC5E3AF4728C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -734,10 +846,13 @@
       <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="G2" s="9" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="3" spans="1:84" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3">
@@ -749,7 +864,9 @@
       <c r="F3" s="3">
         <v>6204</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="3">
+        <v>6346</v>
+      </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -785,7 +902,7 @@
     </row>
     <row r="4" spans="1:84" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
@@ -797,7 +914,9 @@
       <c r="F4" s="3">
         <v>4003</v>
       </c>
-      <c r="G4" s="3"/>
+      <c r="G4" s="3">
+        <v>3937</v>
+      </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -833,7 +952,7 @@
     </row>
     <row r="5" spans="1:84" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
@@ -845,7 +964,9 @@
       <c r="F5" s="3">
         <v>2383</v>
       </c>
-      <c r="G5" s="3"/>
+      <c r="G5" s="3">
+        <v>3401</v>
+      </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -880,24 +1001,26 @@
       <c r="AM5" s="3"/>
     </row>
     <row r="6" spans="1:84" x14ac:dyDescent="0.2">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3">
+      <c r="C6" s="7"/>
+      <c r="D6" s="7">
         <v>13221</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="7">
         <v>13663</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="7">
         <v>13752</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+      <c r="G6" s="7">
+        <v>13640</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
@@ -989,7 +1112,10 @@
         <f>+F12/F6*100000</f>
         <v>48552.937754508435</v>
       </c>
-      <c r="G7" s="3"/>
+      <c r="G7" s="3">
+        <f>+G12/G6*100000</f>
+        <v>52388.3284457478</v>
+      </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -1154,7 +1280,7 @@
     </row>
     <row r="9" spans="1:84" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3">
@@ -1166,7 +1292,9 @@
       <c r="F9" s="3">
         <v>5728</v>
       </c>
-      <c r="G9" s="3"/>
+      <c r="G9" s="3">
+        <v>6005.2430000000004</v>
+      </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -1247,7 +1375,7 @@
     </row>
     <row r="10" spans="1:84" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3">
@@ -1259,7 +1387,9 @@
       <c r="F10" s="3">
         <v>670</v>
       </c>
-      <c r="G10" s="3"/>
+      <c r="G10" s="3">
+        <v>819.55100000000004</v>
+      </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -1340,7 +1470,7 @@
     </row>
     <row r="11" spans="1:84" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3">
@@ -1352,7 +1482,9 @@
       <c r="F11" s="3">
         <v>279</v>
       </c>
-      <c r="G11" s="3"/>
+      <c r="G11" s="3">
+        <v>320.97399999999999</v>
+      </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
@@ -1445,7 +1577,9 @@
       <c r="F12" s="7">
         <v>6677</v>
       </c>
-      <c r="G12" s="3"/>
+      <c r="G12" s="7">
+        <v>7145.768</v>
+      </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
@@ -1526,7 +1660,7 @@
     </row>
     <row r="13" spans="1:84" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3">
@@ -1538,7 +1672,9 @@
       <c r="F13" s="3">
         <v>3330</v>
       </c>
-      <c r="G13" s="3"/>
+      <c r="G13" s="3">
+        <v>3452.971</v>
+      </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
@@ -1619,7 +1755,7 @@
     </row>
     <row r="14" spans="1:84" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3">
@@ -1634,7 +1770,10 @@
         <f>+F12-F13</f>
         <v>3347</v>
       </c>
-      <c r="G14" s="3"/>
+      <c r="G14" s="3">
+        <f>+G12-G13</f>
+        <v>3692.797</v>
+      </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
@@ -1715,7 +1854,7 @@
     </row>
     <row r="15" spans="1:84" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3">
@@ -1727,7 +1866,9 @@
       <c r="F15" s="3">
         <v>561</v>
       </c>
-      <c r="G15" s="3"/>
+      <c r="G15" s="3">
+        <v>642.49</v>
+      </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
@@ -1808,7 +1949,7 @@
     </row>
     <row r="16" spans="1:84" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3">
@@ -1820,7 +1961,9 @@
       <c r="F16" s="3">
         <v>894</v>
       </c>
-      <c r="G16" s="3"/>
+      <c r="G16" s="3">
+        <v>918.86099999999999</v>
+      </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
@@ -1901,7 +2044,7 @@
     </row>
     <row r="17" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3">
@@ -1913,7 +2056,9 @@
       <c r="F17" s="3">
         <v>12</v>
       </c>
-      <c r="G17" s="3"/>
+      <c r="G17" s="3">
+        <v>34.302</v>
+      </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
@@ -1994,7 +2139,7 @@
     </row>
     <row r="18" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3">
@@ -2006,7 +2151,9 @@
       <c r="F18" s="3">
         <v>8</v>
       </c>
-      <c r="G18" s="3"/>
+      <c r="G18" s="3">
+        <v>12.571999999999999</v>
+      </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
@@ -2087,7 +2234,7 @@
     </row>
     <row r="19" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3">
@@ -2102,7 +2249,10 @@
         <f>+F14-SUM(F15:F17)+F18</f>
         <v>1888</v>
       </c>
-      <c r="G19" s="3"/>
+      <c r="G19" s="3">
+        <f>+G14-SUM(G15:G17)+G18</f>
+        <v>2109.7160000000003</v>
+      </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
@@ -2183,7 +2333,7 @@
     </row>
     <row r="20" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3">
@@ -2195,7 +2345,9 @@
       <c r="F20" s="3">
         <v>147</v>
       </c>
-      <c r="G20" s="3"/>
+      <c r="G20" s="3">
+        <v>168.14500000000001</v>
+      </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
@@ -2276,7 +2428,7 @@
     </row>
     <row r="21" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3">
@@ -2288,7 +2440,9 @@
       <c r="F21" s="3">
         <v>146</v>
       </c>
-      <c r="G21" s="3"/>
+      <c r="G21" s="3">
+        <v>214.226</v>
+      </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
@@ -2369,7 +2523,7 @@
     </row>
     <row r="22" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3">
@@ -2384,7 +2538,10 @@
         <f>+F19+F20-F21</f>
         <v>1889</v>
       </c>
-      <c r="G22" s="3"/>
+      <c r="G22" s="3">
+        <f>+G19+G20-G21</f>
+        <v>2063.6350000000002</v>
+      </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
@@ -2465,7 +2622,7 @@
     </row>
     <row r="23" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3">
@@ -2477,7 +2634,9 @@
       <c r="F23" s="3">
         <v>363</v>
       </c>
-      <c r="G23" s="3"/>
+      <c r="G23" s="3">
+        <v>464.11900000000003</v>
+      </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -2558,7 +2717,7 @@
     </row>
     <row r="24" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3">
@@ -2573,7 +2732,10 @@
         <f>+F22-F23</f>
         <v>1526</v>
       </c>
-      <c r="G24" s="3"/>
+      <c r="G24" s="3">
+        <f>+G22-G23</f>
+        <v>1599.5160000000001</v>
+      </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -2737,11 +2899,26 @@
       <c r="CF25" s="3"/>
     </row>
     <row r="26" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="B26" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
+      <c r="D26" s="10">
+        <f t="shared" ref="D26:E26" si="4">+D24/D27</f>
+        <v>5.1357500711019712</v>
+      </c>
+      <c r="E26" s="10">
+        <f t="shared" si="4"/>
+        <v>6.9363204944266634</v>
+      </c>
+      <c r="F26" s="10">
+        <f>+F24/F27</f>
+        <v>8.4898994675731458</v>
+      </c>
+      <c r="G26" s="10">
+        <f>+G24/G27</f>
+        <v>8.9797389473684213</v>
+      </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
@@ -2821,6 +2998,9 @@
       <c r="CF26" s="3"/>
     </row>
     <row r="27" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="B27" s="8" t="s">
+        <v>3</v>
+      </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3">
         <v>182.83600000000001</v>
@@ -2831,7 +3011,9 @@
       <c r="F27" s="3">
         <v>179.74299999999999</v>
       </c>
-      <c r="G27" s="3"/>
+      <c r="G27" s="3">
+        <v>178.125</v>
+      </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
@@ -2995,11 +3177,26 @@
       <c r="CF28" s="3"/>
     </row>
     <row r="29" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="B29" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
+      <c r="D29" s="12" t="e">
+        <f t="shared" ref="D29:G29" si="5">+D6/C6-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E29" s="12">
+        <f t="shared" si="5"/>
+        <v>3.3431661750245922E-2</v>
+      </c>
+      <c r="F29" s="12">
+        <f t="shared" si="5"/>
+        <v>6.5139427651321746E-3</v>
+      </c>
+      <c r="G29" s="12">
+        <f>+G6/F6-1</f>
+        <v>-8.1442699243746697E-3</v>
+      </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -3079,11 +3276,23 @@
       <c r="CF29" s="3"/>
     </row>
     <row r="30" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="B30" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
+      <c r="E30" s="12">
+        <f t="shared" ref="E30:G30" si="6">+E9/D9-1</f>
+        <v>0.18467947234436477</v>
+      </c>
+      <c r="F30" s="12">
+        <f t="shared" si="6"/>
+        <v>0.11896854854463768</v>
+      </c>
+      <c r="G30" s="12">
+        <f>+G9/F9-1</f>
+        <v>4.8401361731843728E-2</v>
+      </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
@@ -3163,11 +3372,26 @@
       <c r="CF30" s="3"/>
     </row>
     <row r="31" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="B31" s="8" t="s">
+        <v>47</v>
+      </c>
       <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
+      <c r="D31" s="12" t="e">
+        <f t="shared" ref="D31:G32" si="7">+D10/C10-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E31" s="12">
+        <f t="shared" si="7"/>
+        <v>0.14629258517034072</v>
+      </c>
+      <c r="F31" s="12">
+        <f t="shared" si="7"/>
+        <v>0.17132867132867124</v>
+      </c>
+      <c r="G31" s="12">
+        <f t="shared" ref="G31:G33" si="8">+G10/F10-1</f>
+        <v>0.22321044776119403</v>
+      </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
@@ -3247,11 +3471,26 @@
       <c r="CF31" s="3"/>
     </row>
     <row r="32" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="B32" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
+      <c r="D32" s="12" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E32" s="12">
+        <f t="shared" si="7"/>
+        <v>1.4545454545454639E-2</v>
+      </c>
+      <c r="F32" s="12">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="12">
+        <f t="shared" si="8"/>
+        <v>0.15044444444444438</v>
+      </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
@@ -3330,12 +3569,27 @@
       <c r="CE32" s="3"/>
       <c r="CF32" s="3"/>
     </row>
-    <row r="33" spans="3:84" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="B33" s="8" t="s">
+        <v>49</v>
+      </c>
       <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
+      <c r="D33" s="13" t="e">
+        <f t="shared" ref="D33:G33" si="9">+D12/C12-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E33" s="13">
+        <f t="shared" si="9"/>
+        <v>0.17173699705593726</v>
+      </c>
+      <c r="F33" s="13">
+        <f t="shared" si="9"/>
+        <v>0.11842546063651582</v>
+      </c>
+      <c r="G33" s="13">
+        <f t="shared" si="8"/>
+        <v>7.0206380110828137E-2</v>
+      </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
@@ -3414,12 +3668,27 @@
       <c r="CE33" s="3"/>
       <c r="CF33" s="3"/>
     </row>
-    <row r="34" spans="3:84" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="B34" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
+      <c r="D34" s="12">
+        <f t="shared" ref="D34:G34" si="10">+D14/D12</f>
+        <v>0.48007850834151128</v>
+      </c>
+      <c r="E34" s="12">
+        <f t="shared" si="10"/>
+        <v>0.49815745393634842</v>
+      </c>
+      <c r="F34" s="12">
+        <f t="shared" si="10"/>
+        <v>0.50127302680844688</v>
+      </c>
+      <c r="G34" s="12">
+        <f>+G14/G12</f>
+        <v>0.51678098141445394</v>
+      </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
@@ -3498,12 +3767,27 @@
       <c r="CE34" s="3"/>
       <c r="CF34" s="3"/>
     </row>
-    <row r="35" spans="3:84" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="B35" s="8" t="s">
+        <v>51</v>
+      </c>
       <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
+      <c r="D35" s="12">
+        <f t="shared" ref="D35:G35" si="11">+D19/D12</f>
+        <v>0.24082433758586849</v>
+      </c>
+      <c r="E35" s="12">
+        <f t="shared" si="11"/>
+        <v>0.27085427135678392</v>
+      </c>
+      <c r="F35" s="12">
+        <f t="shared" si="11"/>
+        <v>0.28276171933503069</v>
+      </c>
+      <c r="G35" s="12">
+        <f>+G19/G12</f>
+        <v>0.29523992382624237</v>
+      </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
@@ -3582,12 +3866,27 @@
       <c r="CE35" s="3"/>
       <c r="CF35" s="3"/>
     </row>
-    <row r="36" spans="3:84" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="B36" s="8" t="s">
+        <v>52</v>
+      </c>
       <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
+      <c r="D36" s="12">
+        <f t="shared" ref="D36:G36" si="12">+D23/D22</f>
+        <v>0.20288624787775891</v>
+      </c>
+      <c r="E36" s="12">
+        <f t="shared" si="12"/>
+        <v>0.21535580524344569</v>
+      </c>
+      <c r="F36" s="12">
+        <f t="shared" si="12"/>
+        <v>0.19216516675489678</v>
+      </c>
+      <c r="G36" s="12">
+        <f>+G23/G22</f>
+        <v>0.22490362879094414</v>
+      </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
@@ -3666,7 +3965,7 @@
       <c r="CE36" s="3"/>
       <c r="CF36" s="3"/>
     </row>
-    <row r="37" spans="3:84" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:84" x14ac:dyDescent="0.2">
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -3750,7 +4049,7 @@
       <c r="CE37" s="3"/>
       <c r="CF37" s="3"/>
     </row>
-    <row r="38" spans="3:84" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:84" x14ac:dyDescent="0.2">
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -3834,7 +4133,7 @@
       <c r="CE38" s="3"/>
       <c r="CF38" s="3"/>
     </row>
-    <row r="39" spans="3:84" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:84" x14ac:dyDescent="0.2">
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -3918,7 +4217,7 @@
       <c r="CE39" s="3"/>
       <c r="CF39" s="3"/>
     </row>
-    <row r="40" spans="3:84" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:84" x14ac:dyDescent="0.2">
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -4002,7 +4301,7 @@
       <c r="CE40" s="3"/>
       <c r="CF40" s="3"/>
     </row>
-    <row r="41" spans="3:84" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:84" x14ac:dyDescent="0.2">
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -4086,7 +4385,7 @@
       <c r="CE41" s="3"/>
       <c r="CF41" s="3"/>
     </row>
-    <row r="42" spans="3:84" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:84" x14ac:dyDescent="0.2">
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -4170,7 +4469,7 @@
       <c r="CE42" s="3"/>
       <c r="CF42" s="3"/>
     </row>
-    <row r="43" spans="3:84" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:84" x14ac:dyDescent="0.2">
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -4254,7 +4553,7 @@
       <c r="CE43" s="3"/>
       <c r="CF43" s="3"/>
     </row>
-    <row r="44" spans="3:84" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:84" x14ac:dyDescent="0.2">
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -4338,7 +4637,7 @@
       <c r="CE44" s="3"/>
       <c r="CF44" s="3"/>
     </row>
-    <row r="45" spans="3:84" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:84" x14ac:dyDescent="0.2">
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4422,7 +4721,7 @@
       <c r="CE45" s="3"/>
       <c r="CF45" s="3"/>
     </row>
-    <row r="46" spans="3:84" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:84" x14ac:dyDescent="0.2">
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -4506,7 +4805,7 @@
       <c r="CE46" s="3"/>
       <c r="CF46" s="3"/>
     </row>
-    <row r="47" spans="3:84" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:84" x14ac:dyDescent="0.2">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -4590,7 +4889,7 @@
       <c r="CE47" s="3"/>
       <c r="CF47" s="3"/>
     </row>
-    <row r="48" spans="3:84" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:84" x14ac:dyDescent="0.2">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
